--- a/data/macro/Japan Interest Rate.xlsx
+++ b/data/macro/Japan Interest Rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/macro/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{761851AC-DDB8-4626-B668-5C062FAA0C6A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E18A3B95-E2FB-874C-B09A-C3947BE9AD52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" xr2:uid="{BD32588E-2B16-4C89-A5B1-1458B27ABC9F}"/>
+    <workbookView xWindow="15520" yWindow="800" windowWidth="18020" windowHeight="19120" xr2:uid="{BD32588E-2B16-4C89-A5B1-1458B27ABC9F}"/>
   </bookViews>
   <sheets>
     <sheet name="JP_interest" sheetId="1" r:id="rId1"/>
@@ -63,21 +63,21 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="181" formatCode="yyyy/mm/dd;@"/>
-    <numFmt numFmtId="183" formatCode="[$-409]h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -85,7 +85,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -93,7 +93,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -102,7 +102,7 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -111,7 +111,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -152,24 +152,24 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -185,9 +185,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -225,7 +225,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -331,7 +331,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -473,7 +473,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -482,33 +482,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFA4B462-8401-43D4-A97D-0B68FA77EED7}">
   <dimension ref="A1:F196"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="8.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="8">
         <v>39492</v>
       </c>
       <c r="B2" s="2">
@@ -523,10 +523,10 @@
       <c r="E2" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F2" s="7"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="8">
         <v>39514</v>
       </c>
       <c r="B3" s="2">
@@ -541,10 +541,10 @@
       <c r="E3" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="8">
         <v>39547</v>
       </c>
       <c r="B4" s="2">
@@ -559,10 +559,10 @@
       <c r="E4" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="8">
         <v>39568</v>
       </c>
       <c r="B5" s="2">
@@ -577,10 +577,10 @@
       <c r="E5" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="8">
         <v>39612</v>
       </c>
       <c r="B6" s="2">
@@ -595,10 +595,10 @@
       <c r="E6" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="8">
         <v>39644</v>
       </c>
       <c r="B7" s="2">
@@ -613,10 +613,10 @@
       <c r="E7" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="8">
         <v>39679</v>
       </c>
       <c r="B8" s="2">
@@ -631,10 +631,10 @@
       <c r="E8" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="8">
         <v>39708</v>
       </c>
       <c r="B9" s="2">
@@ -649,10 +649,10 @@
       <c r="E9" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F9" s="7"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="4">
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="8">
         <v>39728</v>
       </c>
       <c r="B10" s="2">
@@ -667,10 +667,10 @@
       <c r="E10" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F10" s="7"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="8">
         <v>39752</v>
       </c>
       <c r="B11" s="2">
@@ -685,10 +685,10 @@
       <c r="E11" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F11" s="7"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="4">
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="8">
         <v>39773</v>
       </c>
       <c r="B12" s="2">
@@ -703,10 +703,10 @@
       <c r="E12" s="3">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="F12" s="7"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="4">
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="8">
         <v>39784</v>
       </c>
       <c r="B13" s="2">
@@ -721,10 +721,10 @@
       <c r="E13" s="3">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="8">
         <v>39801</v>
       </c>
       <c r="B14" s="2">
@@ -739,10 +739,10 @@
       <c r="E14" s="3">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="8">
         <v>39835</v>
       </c>
       <c r="B15" s="2">
@@ -757,10 +757,10 @@
       <c r="E15" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="8">
         <v>39889</v>
       </c>
       <c r="B16" s="2">
@@ -775,10 +775,10 @@
       <c r="E16" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="8">
         <v>39910</v>
       </c>
       <c r="B17" s="2">
@@ -793,10 +793,10 @@
       <c r="E17" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="8">
         <v>39933</v>
       </c>
       <c r="B18" s="2">
@@ -811,10 +811,10 @@
       <c r="E18" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F18" s="7"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="8">
         <v>39955</v>
       </c>
       <c r="B19" s="2">
@@ -829,10 +829,10 @@
       <c r="E19" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F19" s="7"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="4">
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="8">
         <v>39980</v>
       </c>
       <c r="B20" s="2">
@@ -847,10 +847,10 @@
       <c r="E20" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F20" s="7"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="4">
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="8">
         <v>40009</v>
       </c>
       <c r="B21" s="2">
@@ -865,10 +865,10 @@
       <c r="E21" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F21" s="7"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="4">
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="8">
         <v>40036</v>
       </c>
       <c r="B22" s="2">
@@ -883,10 +883,10 @@
       <c r="E22" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F22" s="7"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="4">
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="8">
         <v>40073</v>
       </c>
       <c r="B23" s="2">
@@ -901,10 +901,10 @@
       <c r="E23" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F23" s="7"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="4">
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="8">
         <v>40100</v>
       </c>
       <c r="B24" s="2">
@@ -919,10 +919,10 @@
       <c r="E24" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F24" s="7"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="4">
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="8">
         <v>40116</v>
       </c>
       <c r="B25" s="2">
@@ -937,10 +937,10 @@
       <c r="E25" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F25" s="7"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="4">
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="8">
         <v>40137</v>
       </c>
       <c r="B26" s="2">
@@ -955,10 +955,10 @@
       <c r="E26" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F26" s="7"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="4">
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="8">
         <v>40148</v>
       </c>
       <c r="B27" s="2">
@@ -970,10 +970,10 @@
       <c r="E27" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F27" s="7"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="4">
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="8">
         <v>40165</v>
       </c>
       <c r="B28" s="2">
@@ -988,10 +988,10 @@
       <c r="E28" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F28" s="7"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="4">
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
         <v>40204</v>
       </c>
       <c r="B29" s="2">
@@ -1006,10 +1006,10 @@
       <c r="E29" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F29" s="7"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="4">
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
         <v>40227</v>
       </c>
       <c r="B30" s="2">
@@ -1024,10 +1024,10 @@
       <c r="E30" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F30" s="7"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="4">
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
         <v>40254</v>
       </c>
       <c r="B31" s="2">
@@ -1042,10 +1042,10 @@
       <c r="E31" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F31" s="7"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="4">
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
         <v>40275</v>
       </c>
       <c r="B32" s="2">
@@ -1060,10 +1060,10 @@
       <c r="E32" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F32" s="7"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="4">
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
         <v>40298</v>
       </c>
       <c r="B33" s="2">
@@ -1078,10 +1078,10 @@
       <c r="E33" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F33" s="7"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="4">
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" s="8">
         <v>40308</v>
       </c>
       <c r="B34" s="2">
@@ -1096,10 +1096,10 @@
       <c r="E34" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F34" s="7"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="4">
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="8">
         <v>40319</v>
       </c>
       <c r="B35" s="2">
@@ -1114,10 +1114,10 @@
       <c r="E35" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F35" s="7"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="4">
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" s="8">
         <v>40344</v>
       </c>
       <c r="B36" s="2">
@@ -1132,10 +1132,10 @@
       <c r="E36" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F36" s="7"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="4">
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="8">
         <v>40374</v>
       </c>
       <c r="B37" s="2">
@@ -1150,10 +1150,10 @@
       <c r="E37" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F37" s="7"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="4">
+      <c r="F37" s="6"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="8">
         <v>40400</v>
       </c>
       <c r="B38" s="2">
@@ -1168,10 +1168,10 @@
       <c r="E38" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F38" s="7"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="4">
+      <c r="F38" s="6"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" s="8">
         <v>40420</v>
       </c>
       <c r="B39" s="2">
@@ -1186,10 +1186,10 @@
       <c r="E39" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F39" s="7"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="4">
+      <c r="F39" s="6"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" s="8">
         <v>40428</v>
       </c>
       <c r="B40" s="2">
@@ -1204,10 +1204,10 @@
       <c r="E40" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F40" s="7"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="4">
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" s="8">
         <v>40456</v>
       </c>
       <c r="B41" s="2">
@@ -1222,10 +1222,10 @@
       <c r="E41" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F41" s="7"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="4">
+      <c r="F41" s="6"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" s="8">
         <v>40479</v>
       </c>
       <c r="B42" s="2">
@@ -1240,10 +1240,10 @@
       <c r="E42" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F42" s="7"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="4">
+      <c r="F42" s="6"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" s="8">
         <v>40487</v>
       </c>
       <c r="B43" s="2">
@@ -1258,10 +1258,10 @@
       <c r="E43" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F43" s="7"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="4">
+      <c r="F43" s="6"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" s="8">
         <v>40533</v>
       </c>
       <c r="B44" s="2">
@@ -1276,10 +1276,10 @@
       <c r="E44" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F44" s="7"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="4">
+      <c r="F44" s="6"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" s="8">
         <v>40568</v>
       </c>
       <c r="B45" s="2">
@@ -1294,10 +1294,10 @@
       <c r="E45" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F45" s="7"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="4">
+      <c r="F45" s="6"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" s="8">
         <v>40589</v>
       </c>
       <c r="B46" s="2">
@@ -1312,10 +1312,10 @@
       <c r="E46" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F46" s="7"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="4">
+      <c r="F46" s="6"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="8">
         <v>40616</v>
       </c>
       <c r="B47" s="2">
@@ -1330,10 +1330,10 @@
       <c r="E47" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F47" s="7"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="4">
+      <c r="F47" s="6"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" s="8">
         <v>40640</v>
       </c>
       <c r="B48" s="2">
@@ -1348,10 +1348,10 @@
       <c r="E48" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F48" s="7"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="4">
+      <c r="F48" s="6"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" s="8">
         <v>40661</v>
       </c>
       <c r="B49" s="2">
@@ -1366,10 +1366,10 @@
       <c r="E49" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F49" s="7"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="4">
+      <c r="F49" s="6"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" s="8">
         <v>40683</v>
       </c>
       <c r="B50" s="2">
@@ -1384,10 +1384,10 @@
       <c r="E50" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F50" s="7"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="4">
+      <c r="F50" s="6"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="8">
         <v>40708</v>
       </c>
       <c r="B51" s="2">
@@ -1402,10 +1402,10 @@
       <c r="E51" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F51" s="7"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="4">
+      <c r="F51" s="6"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52" s="8">
         <v>40736</v>
       </c>
       <c r="B52" s="2">
@@ -1420,10 +1420,10 @@
       <c r="E52" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F52" s="7"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="4">
+      <c r="F52" s="6"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53" s="8">
         <v>40759</v>
       </c>
       <c r="B53" s="2">
@@ -1438,10 +1438,10 @@
       <c r="E53" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F53" s="7"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="4">
+      <c r="F53" s="6"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54" s="8">
         <v>40793</v>
       </c>
       <c r="B54" s="2">
@@ -1456,10 +1456,10 @@
       <c r="E54" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F54" s="7"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="4">
+      <c r="F54" s="6"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" s="8">
         <v>40823</v>
       </c>
       <c r="B55" s="2">
@@ -1474,10 +1474,10 @@
       <c r="E55" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F55" s="7"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="4">
+      <c r="F55" s="6"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" s="8">
         <v>40843</v>
       </c>
       <c r="B56" s="2">
@@ -1492,10 +1492,10 @@
       <c r="E56" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F56" s="7"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="4">
+      <c r="F56" s="6"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57" s="8">
         <v>40863</v>
       </c>
       <c r="B57" s="2">
@@ -1510,10 +1510,10 @@
       <c r="E57" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F57" s="7"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="4">
+      <c r="F57" s="6"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="8">
         <v>40898</v>
       </c>
       <c r="B58" s="2">
@@ -1528,10 +1528,10 @@
       <c r="E58" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F58" s="7"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="4">
+      <c r="F58" s="6"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" s="8">
         <v>40932</v>
       </c>
       <c r="B59" s="2">
@@ -1546,10 +1546,10 @@
       <c r="E59" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F59" s="7"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="4">
+      <c r="F59" s="6"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A60" s="8">
         <v>40953</v>
       </c>
       <c r="B60" s="2">
@@ -1564,10 +1564,10 @@
       <c r="E60" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F60" s="7"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="4">
+      <c r="F60" s="6"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A61" s="8">
         <v>40981</v>
       </c>
       <c r="B61" s="2">
@@ -1582,10 +1582,10 @@
       <c r="E61" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F61" s="7"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="4">
+      <c r="F61" s="6"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A62" s="8">
         <v>41009</v>
       </c>
       <c r="B62" s="2">
@@ -1600,10 +1600,10 @@
       <c r="E62" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F62" s="7"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="4">
+      <c r="F62" s="6"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63" s="8">
         <v>41026</v>
       </c>
       <c r="B63" s="2">
@@ -1618,10 +1618,10 @@
       <c r="E63" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F63" s="7"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="4">
+      <c r="F63" s="6"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A64" s="8">
         <v>41052</v>
       </c>
       <c r="B64" s="2">
@@ -1636,10 +1636,10 @@
       <c r="E64" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F64" s="7"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="4">
+      <c r="F64" s="6"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65" s="8">
         <v>41075</v>
       </c>
       <c r="B65" s="2">
@@ -1654,10 +1654,10 @@
       <c r="E65" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F65" s="7"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="4">
+      <c r="F65" s="6"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" s="8">
         <v>41102</v>
       </c>
       <c r="B66" s="2">
@@ -1672,10 +1672,10 @@
       <c r="E66" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F66" s="7"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="4">
+      <c r="F66" s="6"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67" s="8">
         <v>41130</v>
       </c>
       <c r="B67" s="2">
@@ -1690,10 +1690,10 @@
       <c r="E67" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F67" s="7"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="4">
+      <c r="F67" s="6"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68" s="8">
         <v>41171</v>
       </c>
       <c r="B68" s="2">
@@ -1708,10 +1708,10 @@
       <c r="E68" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F68" s="7"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="4">
+      <c r="F68" s="6"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="8">
         <v>41187</v>
       </c>
       <c r="B69" s="2">
@@ -1726,10 +1726,10 @@
       <c r="E69" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F69" s="7"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="4">
+      <c r="F69" s="6"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70" s="8">
         <v>41212</v>
       </c>
       <c r="B70" s="2">
@@ -1744,10 +1744,10 @@
       <c r="E70" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F70" s="7"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="4">
+      <c r="F70" s="6"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="8">
         <v>41233</v>
       </c>
       <c r="B71" s="2">
@@ -1762,10 +1762,10 @@
       <c r="E71" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F71" s="7"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="4">
+      <c r="F71" s="6"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" s="8">
         <v>41263</v>
       </c>
       <c r="B72" s="2">
@@ -1780,10 +1780,10 @@
       <c r="E72" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F72" s="7"/>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="4">
+      <c r="F72" s="6"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73" s="8">
         <v>41296</v>
       </c>
       <c r="B73" s="2">
@@ -1798,10 +1798,10 @@
       <c r="E73" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F73" s="7"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="4">
+      <c r="F73" s="6"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A74" s="8">
         <v>41319</v>
       </c>
       <c r="B74" s="2">
@@ -1816,10 +1816,10 @@
       <c r="E74" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F74" s="7"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="4">
+      <c r="F74" s="6"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A75" s="8">
         <v>41340</v>
       </c>
       <c r="B75" s="2">
@@ -1834,10 +1834,10 @@
       <c r="E75" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F75" s="7"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="4">
+      <c r="F75" s="6"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A76" s="8">
         <v>41368</v>
       </c>
       <c r="B76" s="2">
@@ -1852,10 +1852,10 @@
       <c r="E76" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F76" s="7"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="4">
+      <c r="F76" s="6"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A77" s="8">
         <v>41390</v>
       </c>
       <c r="B77" s="2">
@@ -1870,10 +1870,10 @@
       <c r="E77" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F77" s="7"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="4">
+      <c r="F77" s="6"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A78" s="8">
         <v>41416</v>
       </c>
       <c r="B78" s="2">
@@ -1888,10 +1888,10 @@
       <c r="E78" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F78" s="7"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="4">
+      <c r="F78" s="6"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A79" s="8">
         <v>41436</v>
       </c>
       <c r="B79" s="2">
@@ -1906,10 +1906,10 @@
       <c r="E79" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F79" s="7"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="4">
+      <c r="F79" s="6"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" s="8">
         <v>41466</v>
       </c>
       <c r="B80" s="2">
@@ -1924,10 +1924,10 @@
       <c r="E80" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F80" s="7"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="4">
+      <c r="F80" s="6"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A81" s="8">
         <v>41494</v>
       </c>
       <c r="B81" s="2">
@@ -1942,10 +1942,10 @@
       <c r="E81" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F81" s="7"/>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="4">
+      <c r="F81" s="6"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A82" s="8">
         <v>41522</v>
       </c>
       <c r="B82" s="2">
@@ -1960,10 +1960,10 @@
       <c r="E82" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F82" s="7"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="4">
+      <c r="F82" s="6"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A83" s="8">
         <v>41551</v>
       </c>
       <c r="B83" s="2">
@@ -1978,10 +1978,10 @@
       <c r="E83" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F83" s="7"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="4">
+      <c r="F83" s="6"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A84" s="8">
         <v>41578</v>
       </c>
       <c r="B84" s="2">
@@ -1996,10 +1996,10 @@
       <c r="E84" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F84" s="7"/>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="4">
+      <c r="F84" s="6"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A85" s="8">
         <v>41599</v>
       </c>
       <c r="B85" s="2">
@@ -2014,10 +2014,10 @@
       <c r="E85" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F85" s="7"/>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="4">
+      <c r="F85" s="6"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A86" s="8">
         <v>41628</v>
       </c>
       <c r="B86" s="2">
@@ -2032,10 +2032,10 @@
       <c r="E86" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F86" s="7"/>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="4">
+      <c r="F86" s="6"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A87" s="8">
         <v>41661</v>
       </c>
       <c r="B87" s="2">
@@ -2050,10 +2050,10 @@
       <c r="E87" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F87" s="7"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="4">
+      <c r="F87" s="6"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A88" s="8">
         <v>41688</v>
       </c>
       <c r="B88" s="2">
@@ -2068,10 +2068,10 @@
       <c r="E88" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F88" s="7"/>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="4">
+      <c r="F88" s="6"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A89" s="8">
         <v>41709</v>
       </c>
       <c r="B89" s="2">
@@ -2086,10 +2086,10 @@
       <c r="E89" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F89" s="7"/>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="4">
+      <c r="F89" s="6"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A90" s="8">
         <v>41737</v>
       </c>
       <c r="B90" s="2">
@@ -2104,10 +2104,10 @@
       <c r="E90" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F90" s="7"/>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="4">
+      <c r="F90" s="6"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A91" s="8">
         <v>41759</v>
       </c>
       <c r="B91" s="2">
@@ -2122,10 +2122,10 @@
       <c r="E91" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F91" s="7"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="4">
+      <c r="F91" s="6"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A92" s="8">
         <v>41780</v>
       </c>
       <c r="B92" s="2">
@@ -2140,10 +2140,10 @@
       <c r="E92" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F92" s="7"/>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="4">
+      <c r="F92" s="6"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A93" s="8">
         <v>41803</v>
       </c>
       <c r="B93" s="2">
@@ -2158,10 +2158,10 @@
       <c r="E93" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F93" s="7"/>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="4">
+      <c r="F93" s="6"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A94" s="8">
         <v>41835</v>
       </c>
       <c r="B94" s="2">
@@ -2176,10 +2176,10 @@
       <c r="E94" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F94" s="7"/>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="4">
+      <c r="F94" s="6"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A95" s="8">
         <v>41859</v>
       </c>
       <c r="B95" s="2">
@@ -2194,10 +2194,10 @@
       <c r="E95" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F95" s="7"/>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="4">
+      <c r="F95" s="6"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A96" s="8">
         <v>41886</v>
       </c>
       <c r="B96" s="2">
@@ -2212,10 +2212,10 @@
       <c r="E96" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F96" s="7"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="4">
+      <c r="F96" s="6"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A97" s="8">
         <v>41919</v>
       </c>
       <c r="B97" s="2">
@@ -2230,10 +2230,10 @@
       <c r="E97" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F97" s="7"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="4">
+      <c r="F97" s="6"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A98" s="8">
         <v>41943</v>
       </c>
       <c r="B98" s="2">
@@ -2248,10 +2248,10 @@
       <c r="E98" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F98" s="7"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="4">
+      <c r="F98" s="6"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A99" s="8">
         <v>41962</v>
       </c>
       <c r="B99" s="2">
@@ -2266,10 +2266,10 @@
       <c r="E99" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F99" s="7"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="4">
+      <c r="F99" s="6"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A100" s="8">
         <v>41992</v>
       </c>
       <c r="B100" s="2">
@@ -2284,10 +2284,10 @@
       <c r="E100" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F100" s="7"/>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="4">
+      <c r="F100" s="6"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A101" s="8">
         <v>42025</v>
       </c>
       <c r="B101" s="2">
@@ -2302,10 +2302,10 @@
       <c r="E101" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F101" s="7"/>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="4">
+      <c r="F101" s="6"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A102" s="8">
         <v>42053</v>
       </c>
       <c r="B102" s="2">
@@ -2320,10 +2320,10 @@
       <c r="E102" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F102" s="7"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="4">
+      <c r="F102" s="6"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A103" s="8">
         <v>42080</v>
       </c>
       <c r="B103" s="2">
@@ -2338,10 +2338,10 @@
       <c r="E103" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F103" s="7"/>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="4">
+      <c r="F103" s="6"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A104" s="8">
         <v>42102</v>
       </c>
       <c r="B104" s="2">
@@ -2356,10 +2356,10 @@
       <c r="E104" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F104" s="7"/>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="4">
+      <c r="F104" s="6"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A105" s="8">
         <v>42124</v>
       </c>
       <c r="B105" s="2">
@@ -2374,10 +2374,10 @@
       <c r="E105" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F105" s="7"/>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="4">
+      <c r="F105" s="6"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A106" s="8">
         <v>42146</v>
       </c>
       <c r="B106" s="2">
@@ -2392,10 +2392,10 @@
       <c r="E106" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F106" s="7"/>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="4">
+      <c r="F106" s="6"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A107" s="8">
         <v>42174</v>
       </c>
       <c r="B107" s="2">
@@ -2410,10 +2410,10 @@
       <c r="E107" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F107" s="7"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="4">
+      <c r="F107" s="6"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A108" s="8">
         <v>42200</v>
       </c>
       <c r="B108" s="2">
@@ -2428,10 +2428,10 @@
       <c r="E108" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F108" s="7"/>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="4">
+      <c r="F108" s="6"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A109" s="8">
         <v>42223</v>
       </c>
       <c r="B109" s="2">
@@ -2446,10 +2446,10 @@
       <c r="E109" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F109" s="7"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="4">
+      <c r="F109" s="6"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A110" s="8">
         <v>42262</v>
       </c>
       <c r="B110" s="2">
@@ -2464,10 +2464,10 @@
       <c r="E110" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F110" s="7"/>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="4">
+      <c r="F110" s="6"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A111" s="8">
         <v>42284</v>
       </c>
       <c r="B111" s="2">
@@ -2482,10 +2482,10 @@
       <c r="E111" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F111" s="7"/>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="4">
+      <c r="F111" s="6"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A112" s="8">
         <v>42307</v>
       </c>
       <c r="B112" s="2">
@@ -2500,10 +2500,10 @@
       <c r="E112" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F112" s="7"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="4">
+      <c r="F112" s="6"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A113" s="8">
         <v>42327</v>
       </c>
       <c r="B113" s="2">
@@ -2518,10 +2518,10 @@
       <c r="E113" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F113" s="7"/>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="4">
+      <c r="F113" s="6"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A114" s="8">
         <v>42356</v>
       </c>
       <c r="B114" s="2">
@@ -2536,10 +2536,10 @@
       <c r="E114" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F114" s="7"/>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="4">
+      <c r="F114" s="6"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A115" s="8">
         <v>42398</v>
       </c>
       <c r="B115" s="2">
@@ -2554,10 +2554,10 @@
       <c r="E115" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F115" s="7"/>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="4">
+      <c r="F115" s="6"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A116" s="8">
         <v>42444</v>
       </c>
       <c r="B116" s="2">
@@ -2572,10 +2572,10 @@
       <c r="E116" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F116" s="7"/>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="4">
+      <c r="F116" s="6"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A117" s="8">
         <v>42488</v>
       </c>
       <c r="B117" s="2">
@@ -2590,10 +2590,10 @@
       <c r="E117" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F117" s="7"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="4">
+      <c r="F117" s="6"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A118" s="8">
         <v>42537</v>
       </c>
       <c r="B118" s="2">
@@ -2608,10 +2608,10 @@
       <c r="E118" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F118" s="7"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="4">
+      <c r="F118" s="6"/>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A119" s="8">
         <v>42580</v>
       </c>
       <c r="B119" s="2">
@@ -2626,10 +2626,10 @@
       <c r="E119" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F119" s="7"/>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="4">
+      <c r="F119" s="6"/>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A120" s="8">
         <v>42634</v>
       </c>
       <c r="B120" s="2">
@@ -2644,10 +2644,10 @@
       <c r="E120" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F120" s="7"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="4">
+      <c r="F120" s="6"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A121" s="8">
         <v>42675</v>
       </c>
       <c r="B121" s="2">
@@ -2662,10 +2662,10 @@
       <c r="E121" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F121" s="7"/>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="4">
+      <c r="F121" s="6"/>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A122" s="8">
         <v>42724</v>
       </c>
       <c r="B122" s="2">
@@ -2680,10 +2680,10 @@
       <c r="E122" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F122" s="7"/>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="4">
+      <c r="F122" s="6"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A123" s="8">
         <v>42766</v>
       </c>
       <c r="B123" s="2">
@@ -2698,10 +2698,10 @@
       <c r="E123" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F123" s="7"/>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="4">
+      <c r="F123" s="6"/>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A124" s="8">
         <v>42810</v>
       </c>
       <c r="B124" s="2">
@@ -2716,10 +2716,10 @@
       <c r="E124" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F124" s="7"/>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="4">
+      <c r="F124" s="6"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A125" s="8">
         <v>42852</v>
       </c>
       <c r="B125" s="2">
@@ -2734,10 +2734,10 @@
       <c r="E125" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F125" s="7"/>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="4">
+      <c r="F125" s="6"/>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A126" s="8">
         <v>42902</v>
       </c>
       <c r="B126" s="2">
@@ -2752,10 +2752,10 @@
       <c r="E126" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F126" s="7"/>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="4">
+      <c r="F126" s="6"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A127" s="8">
         <v>42936</v>
       </c>
       <c r="B127" s="2">
@@ -2770,10 +2770,10 @@
       <c r="E127" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F127" s="7"/>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="4">
+      <c r="F127" s="6"/>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A128" s="8">
         <v>42999</v>
       </c>
       <c r="B128" s="2">
@@ -2788,10 +2788,10 @@
       <c r="E128" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F128" s="7"/>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="4">
+      <c r="F128" s="6"/>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A129" s="8">
         <v>43039</v>
       </c>
       <c r="B129" s="2">
@@ -2806,10 +2806,10 @@
       <c r="E129" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F129" s="7"/>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="4">
+      <c r="F129" s="6"/>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A130" s="8">
         <v>43090</v>
       </c>
       <c r="B130" s="2">
@@ -2824,10 +2824,10 @@
       <c r="E130" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F130" s="7"/>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="4">
+      <c r="F130" s="6"/>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A131" s="8">
         <v>43123</v>
       </c>
       <c r="B131" s="2">
@@ -2842,10 +2842,10 @@
       <c r="E131" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F131" s="7"/>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="4">
+      <c r="F131" s="6"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A132" s="8">
         <v>43168</v>
       </c>
       <c r="B132" s="2">
@@ -2860,10 +2860,10 @@
       <c r="E132" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F132" s="7"/>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="4">
+      <c r="F132" s="6"/>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A133" s="8">
         <v>43217</v>
       </c>
       <c r="B133" s="2">
@@ -2878,10 +2878,10 @@
       <c r="E133" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F133" s="7"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="4">
+      <c r="F133" s="6"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A134" s="8">
         <v>43266</v>
       </c>
       <c r="B134" s="2">
@@ -2896,10 +2896,10 @@
       <c r="E134" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F134" s="7"/>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="4">
+      <c r="F134" s="6"/>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A135" s="8">
         <v>43312</v>
       </c>
       <c r="B135" s="2">
@@ -2914,10 +2914,10 @@
       <c r="E135" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F135" s="7"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="4">
+      <c r="F135" s="6"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A136" s="8">
         <v>43362</v>
       </c>
       <c r="B136" s="2">
@@ -2932,10 +2932,10 @@
       <c r="E136" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F136" s="7"/>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="4">
+      <c r="F136" s="6"/>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A137" s="8">
         <v>43404</v>
       </c>
       <c r="B137" s="2">
@@ -2950,10 +2950,10 @@
       <c r="E137" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F137" s="7"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="4">
+      <c r="F137" s="6"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A138" s="8">
         <v>43454</v>
       </c>
       <c r="B138" s="2">
@@ -2968,10 +2968,10 @@
       <c r="E138" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F138" s="7"/>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="4">
+      <c r="F138" s="6"/>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A139" s="8">
         <v>43488</v>
       </c>
       <c r="B139" s="2">
@@ -2986,10 +2986,10 @@
       <c r="E139" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F139" s="7"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="4">
+      <c r="F139" s="6"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A140" s="8">
         <v>43539</v>
       </c>
       <c r="B140" s="2">
@@ -3004,10 +3004,10 @@
       <c r="E140" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F140" s="7"/>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="4">
+      <c r="F140" s="6"/>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A141" s="8">
         <v>43580</v>
       </c>
       <c r="B141" s="2">
@@ -3022,10 +3022,10 @@
       <c r="E141" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F141" s="7"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="4">
+      <c r="F141" s="6"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A142" s="8">
         <v>43636</v>
       </c>
       <c r="B142" s="2">
@@ -3040,10 +3040,10 @@
       <c r="E142" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F142" s="7"/>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="4">
+      <c r="F142" s="6"/>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A143" s="8">
         <v>43676</v>
       </c>
       <c r="B143" s="2">
@@ -3058,10 +3058,10 @@
       <c r="E143" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F143" s="7"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="4">
+      <c r="F143" s="6"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A144" s="8">
         <v>43727</v>
       </c>
       <c r="B144" s="2">
@@ -3076,10 +3076,10 @@
       <c r="E144" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F144" s="7"/>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="4">
+      <c r="F144" s="6"/>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A145" s="8">
         <v>43769</v>
       </c>
       <c r="B145" s="2">
@@ -3094,10 +3094,10 @@
       <c r="E145" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F145" s="7"/>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="4">
+      <c r="F145" s="6"/>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A146" s="8">
         <v>43818</v>
       </c>
       <c r="B146" s="2">
@@ -3112,10 +3112,10 @@
       <c r="E146" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F146" s="7"/>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="4">
+      <c r="F146" s="6"/>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A147" s="8">
         <v>43851</v>
       </c>
       <c r="B147" s="2">
@@ -3130,10 +3130,10 @@
       <c r="E147" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F147" s="7"/>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="4">
+      <c r="F147" s="6"/>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A148" s="8">
         <v>43906</v>
       </c>
       <c r="B148" s="2">
@@ -3148,10 +3148,10 @@
       <c r="E148" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F148" s="7"/>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="4">
+      <c r="F148" s="6"/>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A149" s="8">
         <v>43948</v>
       </c>
       <c r="B149" s="2">
@@ -3166,10 +3166,10 @@
       <c r="E149" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F149" s="7"/>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A150" s="4">
+      <c r="F149" s="6"/>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A150" s="8">
         <v>43973</v>
       </c>
       <c r="B150" s="2">
@@ -3181,10 +3181,10 @@
       <c r="E150" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F150" s="7"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A151" s="4">
+      <c r="F150" s="6"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A151" s="8">
         <v>43998</v>
       </c>
       <c r="B151" s="2">
@@ -3196,10 +3196,10 @@
       <c r="E151" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F151" s="7"/>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A152" s="4">
+      <c r="F151" s="6"/>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A152" s="8">
         <v>44027</v>
       </c>
       <c r="B152" s="2">
@@ -3214,10 +3214,10 @@
       <c r="E152" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F152" s="7"/>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A153" s="4">
+      <c r="F152" s="6"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A153" s="8">
         <v>44091</v>
       </c>
       <c r="B153" s="2">
@@ -3232,10 +3232,10 @@
       <c r="E153" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F153" s="7"/>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A154" s="4">
+      <c r="F153" s="6"/>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A154" s="8">
         <v>44133</v>
       </c>
       <c r="B154" s="2">
@@ -3250,10 +3250,10 @@
       <c r="E154" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F154" s="7"/>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A155" s="4">
+      <c r="F154" s="6"/>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A155" s="8">
         <v>44183</v>
       </c>
       <c r="B155" s="2">
@@ -3268,10 +3268,10 @@
       <c r="E155" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F155" s="7"/>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A156" s="4">
+      <c r="F155" s="6"/>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A156" s="8">
         <v>44217</v>
       </c>
       <c r="B156" s="2">
@@ -3286,10 +3286,10 @@
       <c r="E156" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F156" s="7"/>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A157" s="4">
+      <c r="F156" s="6"/>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A157" s="8">
         <v>44274</v>
       </c>
       <c r="B157" s="2">
@@ -3304,10 +3304,10 @@
       <c r="E157" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F157" s="7"/>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A158" s="4">
+      <c r="F157" s="6"/>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A158" s="8">
         <v>44313</v>
       </c>
       <c r="B158" s="2">
@@ -3322,10 +3322,10 @@
       <c r="E158" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F158" s="7"/>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A159" s="4">
+      <c r="F158" s="6"/>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A159" s="8">
         <v>44365</v>
       </c>
       <c r="B159" s="2">
@@ -3340,10 +3340,10 @@
       <c r="E159" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F159" s="7"/>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A160" s="4">
+      <c r="F159" s="6"/>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A160" s="8">
         <v>44393</v>
       </c>
       <c r="B160" s="2">
@@ -3358,10 +3358,10 @@
       <c r="E160" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F160" s="7"/>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A161" s="4">
+      <c r="F160" s="6"/>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A161" s="8">
         <v>44461</v>
       </c>
       <c r="B161" s="2">
@@ -3373,10 +3373,10 @@
       <c r="E161" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F161" s="7"/>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A162" s="4">
+      <c r="F161" s="6"/>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162" s="8">
         <v>44497</v>
       </c>
       <c r="B162" s="2">
@@ -3391,10 +3391,10 @@
       <c r="E162" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F162" s="7"/>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A163" s="4">
+      <c r="F162" s="6"/>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A163" s="8">
         <v>44547</v>
       </c>
       <c r="B163" s="2">
@@ -3409,10 +3409,10 @@
       <c r="E163" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F163" s="7"/>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A164" s="4">
+      <c r="F163" s="6"/>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A164" s="8">
         <v>44579</v>
       </c>
       <c r="B164" s="2">
@@ -3427,10 +3427,10 @@
       <c r="E164" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F164" s="7"/>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A165" s="4">
+      <c r="F164" s="6"/>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A165" s="8">
         <v>44638</v>
       </c>
       <c r="B165" s="2">
@@ -3445,10 +3445,10 @@
       <c r="E165" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F165" s="7"/>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A166" s="4">
+      <c r="F165" s="6"/>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A166" s="8">
         <v>44679</v>
       </c>
       <c r="B166" s="2">
@@ -3463,10 +3463,10 @@
       <c r="E166" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F166" s="7"/>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A167" s="4">
+      <c r="F166" s="6"/>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A167" s="8">
         <v>44729</v>
       </c>
       <c r="B167" s="2">
@@ -3481,10 +3481,10 @@
       <c r="E167" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F167" s="7"/>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A168" s="4">
+      <c r="F167" s="6"/>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A168" s="8">
         <v>44729</v>
       </c>
       <c r="B168" s="2">
@@ -3496,10 +3496,10 @@
       <c r="E168" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F168" s="7"/>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A169" s="4">
+      <c r="F168" s="6"/>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A169" s="8">
         <v>44763</v>
       </c>
       <c r="B169" s="2">
@@ -3514,10 +3514,10 @@
       <c r="E169" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F169" s="7"/>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A170" s="4">
+      <c r="F169" s="6"/>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A170" s="8">
         <v>44826</v>
       </c>
       <c r="B170" s="2">
@@ -3532,10 +3532,10 @@
       <c r="E170" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F170" s="7"/>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A171" s="4">
+      <c r="F170" s="6"/>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A171" s="8">
         <v>44862</v>
       </c>
       <c r="B171" s="2">
@@ -3550,10 +3550,10 @@
       <c r="E171" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F171" s="7"/>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A172" s="4">
+      <c r="F171" s="6"/>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A172" s="8">
         <v>44915</v>
       </c>
       <c r="B172" s="2">
@@ -3568,10 +3568,10 @@
       <c r="E172" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F172" s="7"/>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A173" s="4">
+      <c r="F172" s="6"/>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A173" s="8">
         <v>44944</v>
       </c>
       <c r="B173" s="2">
@@ -3586,10 +3586,10 @@
       <c r="E173" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F173" s="7"/>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A174" s="4">
+      <c r="F173" s="6"/>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A174" s="8">
         <v>44995</v>
       </c>
       <c r="B174" s="2">
@@ -3604,10 +3604,10 @@
       <c r="E174" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F174" s="7"/>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A175" s="4">
+      <c r="F174" s="6"/>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A175" s="8">
         <v>45044</v>
       </c>
       <c r="B175" s="2">
@@ -3622,10 +3622,10 @@
       <c r="E175" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F175" s="7"/>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A176" s="4">
+      <c r="F175" s="6"/>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A176" s="8">
         <v>45093</v>
       </c>
       <c r="B176" s="2">
@@ -3640,10 +3640,10 @@
       <c r="E176" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F176" s="7"/>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A177" s="4">
+      <c r="F176" s="6"/>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A177" s="8">
         <v>45135</v>
       </c>
       <c r="B177" s="2">
@@ -3658,10 +3658,10 @@
       <c r="E177" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F177" s="7"/>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A178" s="4">
+      <c r="F177" s="6"/>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A178" s="8">
         <v>45191</v>
       </c>
       <c r="B178" s="2">
@@ -3676,10 +3676,10 @@
       <c r="E178" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F178" s="7"/>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A179" s="4">
+      <c r="F178" s="6"/>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A179" s="8">
         <v>45230</v>
       </c>
       <c r="B179" s="2">
@@ -3694,10 +3694,10 @@
       <c r="E179" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F179" s="7"/>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A180" s="4">
+      <c r="F179" s="6"/>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A180" s="8">
         <v>45279</v>
       </c>
       <c r="B180" s="2">
@@ -3712,10 +3712,10 @@
       <c r="E180" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F180" s="7"/>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A181" s="4">
+      <c r="F180" s="6"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A181" s="8">
         <v>45314</v>
       </c>
       <c r="B181" s="2">
@@ -3730,10 +3730,10 @@
       <c r="E181" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F181" s="7"/>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A182" s="4">
+      <c r="F181" s="6"/>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A182" s="8">
         <v>45370</v>
       </c>
       <c r="B182" s="2">
@@ -3748,10 +3748,10 @@
       <c r="E182" s="3">
         <v>-1E-3</v>
       </c>
-      <c r="F182" s="7"/>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A183" s="4">
+      <c r="F182" s="6"/>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A183" s="8">
         <v>45408</v>
       </c>
       <c r="B183" s="2">
@@ -3766,10 +3766,10 @@
       <c r="E183" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F183" s="7"/>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A184" s="4">
+      <c r="F183" s="6"/>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A184" s="8">
         <v>45457</v>
       </c>
       <c r="B184" s="2">
@@ -3784,10 +3784,10 @@
       <c r="E184" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F184" s="7"/>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A185" s="4">
+      <c r="F184" s="6"/>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A185" s="8">
         <v>45504</v>
       </c>
       <c r="B185" s="2">
@@ -3802,10 +3802,10 @@
       <c r="E185" s="3">
         <v>1E-3</v>
       </c>
-      <c r="F185" s="7"/>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A186" s="4">
+      <c r="F185" s="6"/>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A186" s="8">
         <v>45555</v>
       </c>
       <c r="B186" s="2">
@@ -3820,10 +3820,10 @@
       <c r="E186" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="F186" s="7"/>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A187" s="4">
+      <c r="F186" s="6"/>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A187" s="8">
         <v>45596</v>
       </c>
       <c r="B187" s="2">
@@ -3838,10 +3838,10 @@
       <c r="E187" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="F187" s="7"/>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A188" s="4">
+      <c r="F187" s="6"/>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A188" s="8">
         <v>45645</v>
       </c>
       <c r="B188" s="2">
@@ -3856,10 +3856,10 @@
       <c r="E188" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="F188" s="7"/>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A189" s="4">
+      <c r="F188" s="6"/>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A189" s="8">
         <v>45681</v>
       </c>
       <c r="B189" s="2">
@@ -3874,10 +3874,10 @@
       <c r="E189" s="3">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="F189" s="7"/>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A190" s="4">
+      <c r="F189" s="6"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A190" s="8">
         <v>45735</v>
       </c>
       <c r="B190" s="2">
@@ -3892,10 +3892,10 @@
       <c r="E190" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F190" s="7"/>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A191" s="4">
+      <c r="F190" s="6"/>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A191" s="8">
         <v>45778</v>
       </c>
       <c r="B191" s="2">
@@ -3910,10 +3910,10 @@
       <c r="E191" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F191" s="7"/>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A192" s="4">
+      <c r="F191" s="6"/>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A192" s="8">
         <v>45825</v>
       </c>
       <c r="B192" s="2">
@@ -3928,10 +3928,10 @@
       <c r="E192" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F192" s="7"/>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A193" s="4">
+      <c r="F192" s="6"/>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A193" s="8">
         <v>45869</v>
       </c>
       <c r="B193" s="2">
@@ -3946,10 +3946,10 @@
       <c r="E193" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F193" s="7"/>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A194" s="4">
+      <c r="F193" s="6"/>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A194" s="8">
         <v>45919</v>
       </c>
       <c r="B194" s="2">
@@ -3964,10 +3964,10 @@
       <c r="E194" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F194" s="7"/>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A195" s="4">
+      <c r="F194" s="6"/>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A195" s="8">
         <v>45960</v>
       </c>
       <c r="B195" s="2">
@@ -3982,10 +3982,10 @@
       <c r="E195" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F195" s="7"/>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A196" s="4">
+      <c r="F195" s="6"/>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A196" s="8">
         <v>46010</v>
       </c>
       <c r="B196" s="2">
@@ -4000,7 +4000,7 @@
       <c r="E196" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F196" s="7"/>
+      <c r="F196" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4011,21 +4011,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB9E5B25-827A-49DC-A0E2-CBBE95A45320}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B2" s="8" t="s">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="8" t="s">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B3" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C3" t="s">
